--- a/Data/EXCEL/Transfer/salemon/202206/3135-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/3135-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8352916C-B14B-40E5-929D-C2E9F2CA2825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E99653B6-6C92-4BB3-A781-5DAE12B0401C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="3135-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="10.375" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="9" width="10.875" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-    <col min="12" max="13" width="10.375" customWidth="1"/>
-    <col min="14" max="14" width="10.875" customWidth="1"/>
-    <col min="15" max="15" width="10.375" customWidth="1"/>
-    <col min="16" max="16" width="10.875" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="9" width="11.875" customWidth="1"/>
+    <col min="10" max="10" width="15.25" customWidth="1"/>
+    <col min="11" max="11" width="11.875" customWidth="1"/>
+    <col min="12" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="11.875" customWidth="1"/>
+    <col min="15" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="11.875" customWidth="1"/>
+    <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,431 +1385,431 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>46.2</v>
+        <v>41.9</v>
       </c>
       <c r="C5" s="7">
-        <v>41.9</v>
+        <v>39.5</v>
       </c>
       <c r="D5" s="7">
-        <v>48</v>
+        <v>43.2</v>
       </c>
       <c r="E5" s="7">
-        <v>39.15</v>
+        <v>36.4</v>
       </c>
       <c r="F5" s="8">
-        <v>-4.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G5" s="8">
-        <v>-9.31</v>
+        <v>-5.73</v>
       </c>
       <c r="H5" s="9">
-        <v>2.4900000000000002</v>
+        <v>3.14</v>
       </c>
       <c r="I5" s="10">
-        <v>2.4300000000000002</v>
+        <v>25.7</v>
       </c>
       <c r="J5" s="8">
-        <v>-7.46</v>
+        <v>-3.22</v>
       </c>
       <c r="K5" s="9">
-        <v>18.559999999999999</v>
+        <v>21.69</v>
       </c>
       <c r="L5" s="8">
-        <v>-12.1</v>
+        <v>-10.9</v>
       </c>
       <c r="M5" s="9">
-        <v>2.4900000000000002</v>
+        <v>3.14</v>
       </c>
       <c r="N5" s="10">
-        <v>2.4300000000000002</v>
+        <v>25.7</v>
       </c>
       <c r="O5" s="8">
-        <v>-7.46</v>
+        <v>-3.22</v>
       </c>
       <c r="P5" s="9">
-        <v>18.559999999999999</v>
+        <v>21.69</v>
       </c>
       <c r="Q5" s="8">
-        <v>-12.1</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>53.7</v>
+        <v>46.2</v>
       </c>
       <c r="C6" s="7">
-        <v>46.2</v>
+        <v>41.9</v>
       </c>
       <c r="D6" s="7">
-        <v>57.6</v>
+        <v>48</v>
       </c>
       <c r="E6" s="7">
-        <v>43.5</v>
+        <v>39.15</v>
       </c>
       <c r="F6" s="8">
-        <v>-7.5</v>
+        <v>-4.3</v>
       </c>
       <c r="G6" s="8">
-        <v>-13.97</v>
+        <v>-9.31</v>
       </c>
       <c r="H6" s="9">
-        <v>2.44</v>
-      </c>
-      <c r="I6" s="8">
-        <v>-36.200000000000003</v>
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="I6" s="10">
+        <v>2.4300000000000002</v>
       </c>
       <c r="J6" s="8">
-        <v>-45.9</v>
+        <v>-7.46</v>
       </c>
       <c r="K6" s="9">
-        <v>16.059999999999999</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="L6" s="8">
-        <v>-12.8</v>
+        <v>-12.1</v>
       </c>
       <c r="M6" s="9">
-        <v>2.44</v>
-      </c>
-      <c r="N6" s="8">
-        <v>-36.200000000000003</v>
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="N6" s="10">
+        <v>2.4300000000000002</v>
       </c>
       <c r="O6" s="8">
-        <v>-45.9</v>
+        <v>-7.46</v>
       </c>
       <c r="P6" s="9">
-        <v>16.059999999999999</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="Q6" s="8">
-        <v>-12.8</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>56.1</v>
+        <v>53.7</v>
       </c>
       <c r="C7" s="7">
-        <v>53.7</v>
+        <v>46.2</v>
       </c>
       <c r="D7" s="7">
-        <v>56.4</v>
+        <v>57.6</v>
       </c>
       <c r="E7" s="7">
-        <v>47</v>
+        <v>43.5</v>
       </c>
       <c r="F7" s="8">
-        <v>-2.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G7" s="8">
-        <v>-4.28</v>
+        <v>-13.97</v>
       </c>
       <c r="H7" s="9">
-        <v>3.82</v>
-      </c>
-      <c r="I7" s="10">
-        <v>17.7</v>
+        <v>2.44</v>
+      </c>
+      <c r="I7" s="8">
+        <v>-36.200000000000003</v>
       </c>
       <c r="J7" s="8">
-        <v>-13.5</v>
+        <v>-45.9</v>
       </c>
       <c r="K7" s="9">
-        <v>13.63</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="L7" s="8">
-        <v>-2.02</v>
+        <v>-12.8</v>
       </c>
       <c r="M7" s="9">
-        <v>3.82</v>
-      </c>
-      <c r="N7" s="10">
-        <v>17.7</v>
+        <v>2.44</v>
+      </c>
+      <c r="N7" s="8">
+        <v>-36.200000000000003</v>
       </c>
       <c r="O7" s="8">
-        <v>-13.5</v>
+        <v>-45.9</v>
       </c>
       <c r="P7" s="9">
-        <v>13.63</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="Q7" s="8">
-        <v>-2.02</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>42.8</v>
+        <v>56.1</v>
       </c>
       <c r="C8" s="7">
-        <v>56.1</v>
+        <v>53.7</v>
       </c>
       <c r="D8" s="7">
-        <v>58.1</v>
+        <v>56.4</v>
       </c>
       <c r="E8" s="7">
-        <v>40</v>
-      </c>
-      <c r="F8" s="10">
-        <v>13.3</v>
-      </c>
-      <c r="G8" s="10">
-        <v>31.07</v>
+        <v>47</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-2.4</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-4.28</v>
       </c>
       <c r="H8" s="9">
-        <v>3.24</v>
-      </c>
-      <c r="I8" s="8">
-        <v>-50.6</v>
+        <v>3.82</v>
+      </c>
+      <c r="I8" s="10">
+        <v>17.7</v>
       </c>
       <c r="J8" s="8">
-        <v>-9.3800000000000008</v>
+        <v>-13.5</v>
       </c>
       <c r="K8" s="9">
-        <v>9.81</v>
-      </c>
-      <c r="L8" s="10">
-        <v>3.31</v>
+        <v>13.63</v>
+      </c>
+      <c r="L8" s="8">
+        <v>-2.02</v>
       </c>
       <c r="M8" s="9">
-        <v>3.24</v>
-      </c>
-      <c r="N8" s="8">
-        <v>-50.6</v>
+        <v>3.82</v>
+      </c>
+      <c r="N8" s="10">
+        <v>17.7</v>
       </c>
       <c r="O8" s="8">
-        <v>-9.3800000000000008</v>
+        <v>-13.5</v>
       </c>
       <c r="P8" s="9">
-        <v>9.81</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>3.31</v>
+        <v>13.63</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>49.15</v>
+        <v>42.8</v>
       </c>
       <c r="C9" s="7">
-        <v>42.8</v>
+        <v>56.1</v>
       </c>
       <c r="D9" s="7">
-        <v>53.1</v>
+        <v>58.1</v>
       </c>
       <c r="E9" s="7">
-        <v>40.9</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-6.35</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-12.92</v>
+        <v>40</v>
+      </c>
+      <c r="F9" s="10">
+        <v>13.3</v>
+      </c>
+      <c r="G9" s="10">
+        <v>31.07</v>
       </c>
       <c r="H9" s="9">
-        <v>6.57</v>
-      </c>
-      <c r="I9" s="10">
-        <v>111.3</v>
-      </c>
-      <c r="J9" s="10">
-        <v>11</v>
+        <v>3.24</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-50.6</v>
+      </c>
+      <c r="J9" s="8">
+        <v>-9.3800000000000008</v>
       </c>
       <c r="K9" s="9">
-        <v>6.57</v>
+        <v>9.81</v>
       </c>
       <c r="L9" s="10">
-        <v>11</v>
+        <v>3.31</v>
       </c>
       <c r="M9" s="9">
-        <v>6.57</v>
-      </c>
-      <c r="N9" s="10">
-        <v>111.3</v>
-      </c>
-      <c r="O9" s="10">
-        <v>11</v>
+        <v>3.24</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-50.6</v>
+      </c>
+      <c r="O9" s="8">
+        <v>-9.3800000000000008</v>
       </c>
       <c r="P9" s="9">
-        <v>6.57</v>
+        <v>9.81</v>
       </c>
       <c r="Q9" s="10">
-        <v>11</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>55.1</v>
+        <v>49.15</v>
       </c>
       <c r="C10" s="7">
-        <v>49.15</v>
+        <v>42.8</v>
       </c>
       <c r="D10" s="7">
-        <v>62</v>
+        <v>53.1</v>
       </c>
       <c r="E10" s="7">
-        <v>45.5</v>
+        <v>40.9</v>
       </c>
       <c r="F10" s="8">
-        <v>-5.95</v>
+        <v>-6.35</v>
       </c>
       <c r="G10" s="8">
-        <v>-10.8</v>
+        <v>-12.92</v>
       </c>
       <c r="H10" s="9">
-        <v>3.11</v>
+        <v>6.57</v>
       </c>
       <c r="I10" s="10">
-        <v>9.24</v>
-      </c>
-      <c r="J10" s="8">
-        <v>-20.3</v>
+        <v>111.3</v>
+      </c>
+      <c r="J10" s="10">
+        <v>11</v>
       </c>
       <c r="K10" s="9">
-        <v>43.79</v>
+        <v>6.57</v>
       </c>
       <c r="L10" s="10">
-        <v>8.64</v>
+        <v>11</v>
       </c>
       <c r="M10" s="9">
-        <v>3.11</v>
+        <v>6.57</v>
       </c>
       <c r="N10" s="10">
-        <v>9.24</v>
-      </c>
-      <c r="O10" s="8">
-        <v>-20.3</v>
+        <v>111.3</v>
+      </c>
+      <c r="O10" s="10">
+        <v>11</v>
       </c>
       <c r="P10" s="9">
-        <v>43.79</v>
+        <v>6.57</v>
       </c>
       <c r="Q10" s="10">
-        <v>8.64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>66.2</v>
+        <v>55.1</v>
       </c>
       <c r="C11" s="7">
-        <v>55.1</v>
+        <v>49.15</v>
       </c>
       <c r="D11" s="7">
-        <v>72.400000000000006</v>
+        <v>62</v>
       </c>
       <c r="E11" s="7">
-        <v>50.2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>52.1</v>
-      </c>
-      <c r="G11" s="10">
-        <v>1736.67</v>
+        <v>45.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>-5.95</v>
+      </c>
+      <c r="G11" s="8">
+        <v>-10.8</v>
       </c>
       <c r="H11" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-15.9</v>
+        <v>3.11</v>
+      </c>
+      <c r="I11" s="10">
+        <v>9.24</v>
       </c>
       <c r="J11" s="8">
-        <v>-29.1</v>
+        <v>-20.3</v>
       </c>
       <c r="K11" s="9">
-        <v>40.69</v>
+        <v>43.79</v>
       </c>
       <c r="L11" s="10">
-        <v>11.8</v>
+        <v>8.64</v>
       </c>
       <c r="M11" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-15.9</v>
+        <v>3.11</v>
+      </c>
+      <c r="N11" s="10">
+        <v>9.24</v>
       </c>
       <c r="O11" s="8">
-        <v>-29.1</v>
+        <v>-20.3</v>
       </c>
       <c r="P11" s="9">
-        <v>40.69</v>
+        <v>43.79</v>
       </c>
       <c r="Q11" s="10">
-        <v>11.8</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>17</v>
+        <v>44501</v>
+      </c>
+      <c r="B12" s="7">
+        <v>66.2</v>
+      </c>
+      <c r="C12" s="7">
+        <v>55.1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="E12" s="7">
+        <v>50.2</v>
+      </c>
+      <c r="F12" s="10">
+        <v>52.1</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1736.67</v>
       </c>
       <c r="H12" s="9">
-        <v>3.38</v>
-      </c>
-      <c r="I12" s="10">
-        <v>8.52</v>
+        <v>2.84</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-15.9</v>
       </c>
       <c r="J12" s="8">
-        <v>-33.299999999999997</v>
+        <v>-29.1</v>
       </c>
       <c r="K12" s="9">
-        <v>37.840000000000003</v>
+        <v>40.69</v>
       </c>
       <c r="L12" s="10">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="M12" s="9">
-        <v>3.38</v>
-      </c>
-      <c r="N12" s="10">
-        <v>8.52</v>
+        <v>2.84</v>
+      </c>
+      <c r="N12" s="8">
+        <v>-15.9</v>
       </c>
       <c r="O12" s="8">
-        <v>-33.299999999999997</v>
+        <v>-29.1</v>
       </c>
       <c r="P12" s="9">
-        <v>37.840000000000003</v>
+        <v>40.69</v>
       </c>
       <c r="Q12" s="10">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1830,39 +1830,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>3.12</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-17.2</v>
+        <v>3.38</v>
+      </c>
+      <c r="I13" s="10">
+        <v>8.52</v>
       </c>
       <c r="J13" s="8">
-        <v>-39.5</v>
+        <v>-33.299999999999997</v>
       </c>
       <c r="K13" s="9">
-        <v>34.46</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="L13" s="10">
-        <v>26.1</v>
+        <v>16.8</v>
       </c>
       <c r="M13" s="9">
-        <v>3.12</v>
-      </c>
-      <c r="N13" s="8">
-        <v>-17.2</v>
+        <v>3.38</v>
+      </c>
+      <c r="N13" s="10">
+        <v>8.52</v>
       </c>
       <c r="O13" s="8">
-        <v>-39.5</v>
+        <v>-33.299999999999997</v>
       </c>
       <c r="P13" s="9">
-        <v>34.46</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="Q13" s="10">
-        <v>26.1</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1883,39 +1883,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
-        <v>3.77</v>
-      </c>
-      <c r="I14" s="10">
-        <v>18.5</v>
-      </c>
-      <c r="J14" s="10">
-        <v>43.9</v>
+        <v>3.12</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-17.2</v>
+      </c>
+      <c r="J14" s="8">
+        <v>-39.5</v>
       </c>
       <c r="K14" s="9">
-        <v>31.34</v>
+        <v>34.46</v>
       </c>
       <c r="L14" s="10">
-        <v>41.4</v>
+        <v>26.1</v>
       </c>
       <c r="M14" s="9">
-        <v>3.77</v>
-      </c>
-      <c r="N14" s="10">
-        <v>18.5</v>
-      </c>
-      <c r="O14" s="10">
-        <v>43.9</v>
+        <v>3.12</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-17.2</v>
+      </c>
+      <c r="O14" s="8">
+        <v>-39.5</v>
       </c>
       <c r="P14" s="9">
-        <v>31.34</v>
+        <v>34.46</v>
       </c>
       <c r="Q14" s="10">
-        <v>41.4</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1936,125 +1936,125 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>3.18</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>17</v>
+        <v>3.77</v>
+      </c>
+      <c r="I15" s="10">
+        <v>18.5</v>
       </c>
       <c r="J15" s="10">
-        <v>71.7</v>
+        <v>43.9</v>
       </c>
       <c r="K15" s="9">
-        <v>27.57</v>
+        <v>31.34</v>
       </c>
       <c r="L15" s="10">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="M15" s="9">
-        <v>3.18</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>17</v>
+        <v>3.77</v>
+      </c>
+      <c r="N15" s="10">
+        <v>18.5</v>
       </c>
       <c r="O15" s="10">
-        <v>71.7</v>
+        <v>43.9</v>
       </c>
       <c r="P15" s="9">
-        <v>27.57</v>
+        <v>31.34</v>
       </c>
       <c r="Q15" s="10">
-        <v>41</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>38261</v>
-      </c>
-      <c r="B16" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="C16" s="7">
-        <v>10</v>
-      </c>
-      <c r="D16" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="E16" s="7">
-        <v>9.67</v>
-      </c>
-      <c r="F16" s="8">
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="G16" s="8">
-        <v>-18.7</v>
+        <v>44378</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="H16" s="9">
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="I16" s="10">
-        <v>14.3</v>
+        <v>3.18</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J16" s="10">
-        <v>132.5</v>
+        <v>71.7</v>
       </c>
       <c r="K16" s="9">
-        <v>4.5199999999999996</v>
+        <v>27.57</v>
       </c>
       <c r="L16" s="10">
-        <v>83</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="M16" s="9">
+        <v>3.18</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>17</v>
+      <c r="O16" s="10">
+        <v>71.7</v>
+      </c>
+      <c r="P16" s="9">
+        <v>27.57</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>38231</v>
+        <v>38261</v>
       </c>
       <c r="B17" s="7">
         <v>12.3</v>
       </c>
       <c r="C17" s="7">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="D17" s="7">
         <v>12.3</v>
       </c>
       <c r="E17" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
+        <v>9.67</v>
+      </c>
+      <c r="F17" s="8">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="G17" s="8">
+        <v>-18.7</v>
       </c>
       <c r="H17" s="9">
-        <v>0.45300000000000001</v>
-      </c>
-      <c r="I17" s="8">
-        <v>-13.4</v>
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="I17" s="10">
+        <v>14.3</v>
       </c>
       <c r="J17" s="10">
-        <v>104.5</v>
+        <v>132.5</v>
       </c>
       <c r="K17" s="9">
-        <v>4</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="L17" s="10">
-        <v>78.099999999999994</v>
+        <v>83</v>
       </c>
       <c r="M17" s="9" t="s">
         <v>17</v>
@@ -2074,40 +2074,40 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>38200</v>
+        <v>38231</v>
       </c>
       <c r="B18" s="7">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="C18" s="7">
         <v>12.3</v>
       </c>
       <c r="D18" s="7">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="E18" s="7">
         <v>12.3</v>
       </c>
-      <c r="F18" s="8">
-        <v>-0.1</v>
-      </c>
-      <c r="G18" s="8">
-        <v>-0.81</v>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
       </c>
       <c r="H18" s="9">
-        <v>0.52300000000000002</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="I18" s="8">
-        <v>-11.3</v>
+        <v>-13.4</v>
       </c>
       <c r="J18" s="10">
-        <v>114.5</v>
+        <v>104.5</v>
       </c>
       <c r="K18" s="9">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="L18" s="10">
-        <v>75.2</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>17</v>
@@ -2127,40 +2127,40 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>38169</v>
+        <v>38200</v>
       </c>
       <c r="B19" s="7">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C19" s="7">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="D19" s="7">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="E19" s="7">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F19" s="8">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G19" s="8">
-        <v>-3.13</v>
+        <v>-0.81</v>
       </c>
       <c r="H19" s="9">
-        <v>0.59</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="I19" s="8">
-        <v>-10.5</v>
+        <v>-11.3</v>
       </c>
       <c r="J19" s="10">
-        <v>162.19999999999999</v>
+        <v>114.5</v>
       </c>
       <c r="K19" s="9">
-        <v>3.03</v>
+        <v>3.55</v>
       </c>
       <c r="L19" s="10">
-        <v>69.8</v>
+        <v>75.2</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>17</v>
@@ -2180,40 +2180,40 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>38139</v>
+        <v>38169</v>
       </c>
       <c r="B20" s="7">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="C20" s="7">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="D20" s="7">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="E20" s="7">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="F20" s="8">
-        <v>-1.2</v>
+        <v>-0.4</v>
       </c>
       <c r="G20" s="8">
-        <v>-8.57</v>
+        <v>-3.13</v>
       </c>
       <c r="H20" s="9">
-        <v>0.65900000000000003</v>
-      </c>
-      <c r="I20" s="10">
-        <v>48.6</v>
+        <v>0.59</v>
+      </c>
+      <c r="I20" s="8">
+        <v>-10.5</v>
       </c>
       <c r="J20" s="10">
-        <v>81</v>
+        <v>162.19999999999999</v>
       </c>
       <c r="K20" s="9">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="L20" s="10">
-        <v>56.5</v>
+        <v>69.8</v>
       </c>
       <c r="M20" s="9" t="s">
         <v>17</v>
@@ -2233,40 +2233,40 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>38108</v>
+        <v>38139</v>
       </c>
       <c r="B21" s="7">
-        <v>13.04</v>
+        <v>14</v>
       </c>
       <c r="C21" s="7">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="D21" s="7">
         <v>14</v>
       </c>
       <c r="E21" s="7">
-        <v>13.04</v>
-      </c>
-      <c r="F21" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="G21" s="10">
-        <v>7.36</v>
+        <v>12.8</v>
+      </c>
+      <c r="F21" s="8">
+        <v>-1.2</v>
+      </c>
+      <c r="G21" s="8">
+        <v>-8.57</v>
       </c>
       <c r="H21" s="9">
-        <v>0.443</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="I21" s="10">
-        <v>87</v>
+        <v>48.6</v>
       </c>
       <c r="J21" s="10">
-        <v>117.3</v>
+        <v>81</v>
       </c>
       <c r="K21" s="9">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="L21" s="10">
-        <v>69.3</v>
+        <v>56.5</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>17</v>
@@ -2286,40 +2286,40 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>38078</v>
+        <v>38108</v>
       </c>
       <c r="B22" s="7">
-        <v>15</v>
+        <v>13.04</v>
       </c>
       <c r="C22" s="7">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7">
+        <v>14</v>
+      </c>
+      <c r="E22" s="7">
         <v>13.04</v>
       </c>
-      <c r="D22" s="7">
-        <v>15</v>
-      </c>
-      <c r="E22" s="7">
-        <v>13</v>
-      </c>
-      <c r="F22" s="8">
-        <v>-1.96</v>
-      </c>
-      <c r="G22" s="8">
-        <v>-13.07</v>
+      <c r="F22" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="G22" s="10">
+        <v>7.36</v>
       </c>
       <c r="H22" s="9">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="I22" s="8">
-        <v>-36.4</v>
+        <v>0.443</v>
+      </c>
+      <c r="I22" s="10">
+        <v>87</v>
       </c>
       <c r="J22" s="10">
-        <v>18.2</v>
+        <v>117.3</v>
       </c>
       <c r="K22" s="9">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="L22" s="10">
-        <v>57.8</v>
+        <v>69.3</v>
       </c>
       <c r="M22" s="9" t="s">
         <v>17</v>
@@ -2339,40 +2339,40 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>38047</v>
+        <v>38078</v>
       </c>
       <c r="B23" s="7">
         <v>15</v>
       </c>
       <c r="C23" s="7">
+        <v>13.04</v>
+      </c>
+      <c r="D23" s="7">
         <v>15</v>
       </c>
-      <c r="D23" s="7">
-        <v>16</v>
-      </c>
       <c r="E23" s="7">
-        <v>14.4</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F23" s="8">
+        <v>-1.96</v>
+      </c>
+      <c r="G23" s="8">
+        <v>-13.07</v>
       </c>
       <c r="H23" s="9">
-        <v>0.372</v>
-      </c>
-      <c r="I23" s="10">
-        <v>23.2</v>
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="I23" s="8">
+        <v>-36.4</v>
       </c>
       <c r="J23" s="10">
-        <v>69.8</v>
+        <v>18.2</v>
       </c>
       <c r="K23" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="L23" s="10">
-        <v>70.099999999999994</v>
+        <v>57.8</v>
       </c>
       <c r="M23" s="9" t="s">
         <v>17</v>
@@ -2392,40 +2392,40 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>38018</v>
+        <v>38047</v>
       </c>
       <c r="B24" s="7">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="C24" s="7">
         <v>15</v>
       </c>
       <c r="D24" s="7">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="E24" s="7">
-        <v>14.1</v>
-      </c>
-      <c r="F24" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G24" s="10">
-        <v>1.35</v>
+        <v>14.4</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
       </c>
       <c r="H24" s="9">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="I24" s="8">
-        <v>-28.4</v>
+        <v>0.372</v>
+      </c>
+      <c r="I24" s="10">
+        <v>23.2</v>
       </c>
       <c r="J24" s="10">
-        <v>21</v>
+        <v>69.8</v>
       </c>
       <c r="K24" s="9">
-        <v>0.72499999999999998</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L24" s="10">
-        <v>70.2</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="M24" s="9" t="s">
         <v>17</v>
@@ -2445,40 +2445,40 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>37987</v>
+        <v>38018</v>
       </c>
       <c r="B25" s="7">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="C25" s="7">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="D25" s="7">
-        <v>16.3</v>
+        <v>15.1</v>
       </c>
       <c r="E25" s="7">
-        <v>14</v>
-      </c>
-      <c r="F25" s="8">
-        <v>-0.4</v>
-      </c>
-      <c r="G25" s="8">
-        <v>-2.63</v>
+        <v>14.1</v>
+      </c>
+      <c r="F25" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="G25" s="10">
+        <v>1.35</v>
       </c>
       <c r="H25" s="9">
-        <v>0.42299999999999999</v>
-      </c>
-      <c r="I25" s="10">
-        <v>21.1</v>
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="I25" s="8">
+        <v>-28.4</v>
       </c>
       <c r="J25" s="10">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="K25" s="9">
-        <v>0.42299999999999999</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="L25" s="10">
-        <v>140</v>
+        <v>70.2</v>
       </c>
       <c r="M25" s="9" t="s">
         <v>17</v>
@@ -2498,40 +2498,40 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>37956</v>
+        <v>37987</v>
       </c>
       <c r="B26" s="7">
-        <v>12.8</v>
+        <v>15.2</v>
       </c>
       <c r="C26" s="7">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="D26" s="7">
-        <v>15.2</v>
+        <v>16.3</v>
       </c>
       <c r="E26" s="7">
-        <v>11.6</v>
-      </c>
-      <c r="F26" s="10">
-        <v>2.4</v>
-      </c>
-      <c r="G26" s="10">
-        <v>18.75</v>
+        <v>14</v>
+      </c>
+      <c r="F26" s="8">
+        <v>-0.4</v>
+      </c>
+      <c r="G26" s="8">
+        <v>-2.63</v>
       </c>
       <c r="H26" s="9">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="I26" s="8">
-        <v>-16.5</v>
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="I26" s="10">
+        <v>21.1</v>
       </c>
       <c r="J26" s="10">
-        <v>1741.9</v>
+        <v>140</v>
       </c>
       <c r="K26" s="9">
-        <v>3.24</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="L26" s="10">
-        <v>82.7</v>
+        <v>140</v>
       </c>
       <c r="M26" s="9" t="s">
         <v>17</v>
@@ -2551,40 +2551,40 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>37926</v>
+        <v>37956</v>
       </c>
       <c r="B27" s="7">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="C27" s="7">
-        <v>12.8</v>
+        <v>15.2</v>
       </c>
       <c r="D27" s="7">
-        <v>13</v>
+        <v>15.2</v>
       </c>
       <c r="E27" s="7">
-        <v>12.8</v>
-      </c>
-      <c r="F27" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="G27" s="8">
-        <v>-1.54</v>
+        <v>11.6</v>
+      </c>
+      <c r="F27" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="G27" s="10">
+        <v>18.75</v>
       </c>
       <c r="H27" s="9">
-        <v>0.41799999999999998</v>
-      </c>
-      <c r="I27" s="10">
-        <v>87.4</v>
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="I27" s="8">
+        <v>-16.5</v>
       </c>
       <c r="J27" s="10">
-        <v>206.5</v>
+        <v>1741.9</v>
       </c>
       <c r="K27" s="9">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="L27" s="10">
-        <v>66.599999999999994</v>
+        <v>82.7</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>17</v>
@@ -2604,40 +2604,40 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>37895</v>
+        <v>37926</v>
       </c>
       <c r="B28" s="7">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="C28" s="7">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="D28" s="7">
         <v>13</v>
       </c>
       <c r="E28" s="7">
-        <v>12.7</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G28" s="10">
-        <v>2.36</v>
+        <v>12.8</v>
+      </c>
+      <c r="F28" s="8">
+        <v>-0.2</v>
+      </c>
+      <c r="G28" s="8">
+        <v>-1.54</v>
       </c>
       <c r="H28" s="9">
-        <v>0.223</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="I28" s="10">
-        <v>0.56000000000000005</v>
+        <v>87.4</v>
       </c>
       <c r="J28" s="10">
-        <v>16659.400000000001</v>
+        <v>206.5</v>
       </c>
       <c r="K28" s="9">
-        <v>2.4700000000000002</v>
+        <v>2.89</v>
       </c>
       <c r="L28" s="10">
-        <v>52.7</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="M28" s="9" t="s">
         <v>17</v>
@@ -2657,40 +2657,40 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>37865</v>
+        <v>37895</v>
       </c>
       <c r="B29" s="7">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="C29" s="7">
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
+        <v>13</v>
+      </c>
+      <c r="E29" s="7">
         <v>12.7</v>
       </c>
-      <c r="D29" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="E29" s="7">
-        <v>12.5</v>
-      </c>
-      <c r="F29" s="8">
-        <v>-1.8</v>
-      </c>
-      <c r="G29" s="8">
-        <v>-12.41</v>
+      <c r="F29" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G29" s="10">
+        <v>2.36</v>
       </c>
       <c r="H29" s="9">
-        <v>0.222</v>
-      </c>
-      <c r="I29" s="8">
-        <v>-9.1300000000000008</v>
+        <v>0.223</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0.56000000000000005</v>
       </c>
       <c r="J29" s="10">
-        <v>45.5</v>
+        <v>16659.400000000001</v>
       </c>
       <c r="K29" s="9">
-        <v>2.25</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="L29" s="10">
-        <v>40.4</v>
+        <v>52.7</v>
       </c>
       <c r="M29" s="9" t="s">
         <v>17</v>
@@ -2710,40 +2710,40 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>37834</v>
+        <v>37865</v>
       </c>
       <c r="B30" s="7">
-        <v>19.600000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="C30" s="7">
+        <v>12.7</v>
+      </c>
+      <c r="D30" s="7">
         <v>14.5</v>
       </c>
-      <c r="D30" s="7">
-        <v>19.600000000000001</v>
-      </c>
       <c r="E30" s="7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F30" s="8">
-        <v>-5.0999999999999996</v>
+        <v>-1.8</v>
       </c>
       <c r="G30" s="8">
-        <v>-26.02</v>
+        <v>-12.41</v>
       </c>
       <c r="H30" s="9">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="I30" s="10">
-        <v>8.4499999999999993</v>
+        <v>0.222</v>
+      </c>
+      <c r="I30" s="8">
+        <v>-9.1300000000000008</v>
       </c>
       <c r="J30" s="10">
-        <v>1502.8</v>
+        <v>45.5</v>
       </c>
       <c r="K30" s="9">
-        <v>2.0299999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="L30" s="10">
-        <v>38.4</v>
+        <v>40.4</v>
       </c>
       <c r="M30" s="9" t="s">
         <v>17</v>
@@ -2763,40 +2763,40 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>37803</v>
+        <v>37834</v>
       </c>
       <c r="B31" s="7">
-        <v>20.09</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="C31" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="D31" s="7">
         <v>19.600000000000001</v>
       </c>
-      <c r="D31" s="7">
-        <v>20.09</v>
-      </c>
       <c r="E31" s="7">
-        <v>19.600000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="F31" s="8">
-        <v>-0.49</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="G31" s="8">
-        <v>-2.44</v>
+        <v>-26.02</v>
       </c>
       <c r="H31" s="9">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="I31" s="8">
-        <v>-38.200000000000003</v>
-      </c>
-      <c r="J31" s="8">
-        <v>-16.600000000000001</v>
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="I31" s="10">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="J31" s="10">
+        <v>1502.8</v>
       </c>
       <c r="K31" s="9">
-        <v>1.78</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L31" s="10">
-        <v>23</v>
+        <v>38.4</v>
       </c>
       <c r="M31" s="9" t="s">
         <v>17</v>
@@ -2816,40 +2816,40 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>37773</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>17</v>
+        <v>37803</v>
+      </c>
+      <c r="B32" s="7">
+        <v>20.09</v>
+      </c>
+      <c r="C32" s="7">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D32" s="7">
+        <v>20.09</v>
+      </c>
+      <c r="E32" s="7">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-0.49</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-2.44</v>
       </c>
       <c r="H32" s="9">
-        <v>0.36399999999999999</v>
-      </c>
-      <c r="I32" s="10">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="J32" s="10">
-        <v>154.1</v>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="I32" s="8">
+        <v>-38.200000000000003</v>
+      </c>
+      <c r="J32" s="8">
+        <v>-16.600000000000001</v>
       </c>
       <c r="K32" s="9">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="L32" s="10">
-        <v>19.7</v>
+        <v>23</v>
       </c>
       <c r="M32" s="9" t="s">
         <v>17</v>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>37742</v>
+        <v>37773</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2890,19 +2890,19 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
-        <v>0.20399999999999999</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="I33" s="10">
-        <v>1.66</v>
-      </c>
-      <c r="J33" s="8">
-        <v>-40.799999999999997</v>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="J33" s="10">
+        <v>154.1</v>
       </c>
       <c r="K33" s="9">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="L33" s="10">
-        <v>1.36</v>
+        <v>19.7</v>
       </c>
       <c r="M33" s="9" t="s">
         <v>17</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>37712</v>
+        <v>37742</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2943,19 +2943,19 @@
         <v>17</v>
       </c>
       <c r="H34" s="9">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="I34" s="8">
-        <v>-8.52</v>
-      </c>
-      <c r="J34" s="10">
-        <v>31.2</v>
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1.66</v>
+      </c>
+      <c r="J34" s="8">
+        <v>-40.799999999999997</v>
       </c>
       <c r="K34" s="9">
-        <v>0.84599999999999997</v>
+        <v>1.05</v>
       </c>
       <c r="L34" s="10">
-        <v>22.4</v>
+        <v>1.36</v>
       </c>
       <c r="M34" s="9" t="s">
         <v>17</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>37681</v>
+        <v>37712</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2996,19 +2996,19 @@
         <v>17</v>
       </c>
       <c r="H35" s="9">
-        <v>0.219</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="I35" s="8">
-        <v>-12.2</v>
-      </c>
-      <c r="J35" s="8">
-        <v>-0.14000000000000001</v>
+        <v>-8.52</v>
+      </c>
+      <c r="J35" s="10">
+        <v>31.2</v>
       </c>
       <c r="K35" s="9">
-        <v>0.64500000000000002</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="L35" s="10">
-        <v>19.899999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="M35" s="9" t="s">
         <v>17</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>37653</v>
+        <v>37681</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3049,19 +3049,19 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="I36" s="10">
-        <v>41.9</v>
-      </c>
-      <c r="J36" s="10">
-        <v>80.400000000000006</v>
+        <v>0.219</v>
+      </c>
+      <c r="I36" s="8">
+        <v>-12.2</v>
+      </c>
+      <c r="J36" s="8">
+        <v>-0.14000000000000001</v>
       </c>
       <c r="K36" s="9">
-        <v>0.42599999999999999</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="L36" s="10">
-        <v>33.700000000000003</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="M36" s="9" t="s">
         <v>17</v>
@@ -3081,54 +3081,107 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
+        <v>37653</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="I37" s="10">
+        <v>41.9</v>
+      </c>
+      <c r="J37" s="10">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="K37" s="9">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="L37" s="10">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q37" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
         <v>37622</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="9">
+      <c r="B38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="9">
         <v>0.17599999999999999</v>
       </c>
-      <c r="I37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="8">
+      <c r="I38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="8">
         <v>-2.23</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K38" s="9">
         <v>0.17599999999999999</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L38" s="8">
         <v>-2.23</v>
       </c>
-      <c r="M37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q37" s="9" t="s">
+      <c r="M38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q38" s="9" t="s">
         <v>17</v>
       </c>
     </row>
